--- a/data/trans_bre/IMC_inf_MED_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 12,01</t>
+          <t>-16,89; 11,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 3,95</t>
+          <t>-26,29; 4,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 22,82</t>
+          <t>-11,47; 22,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 29,45</t>
+          <t>-29,7; 28,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,14; 9,19</t>
+          <t>-50,15; 10,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 120,34</t>
+          <t>-37,57; 138,77</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,77; -2,22</t>
+          <t>-29,66; -1,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,43; -3,53</t>
+          <t>-27,24; -4,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,9; -0,86</t>
+          <t>-35,47; -1,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,95; -3,82</t>
+          <t>-46,44; -3,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,62; -8,93</t>
+          <t>-64,78; -11,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,98; -2,58</t>
+          <t>-68,76; -3,58</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-36,87; -8,69</t>
+          <t>-36,81; -6,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 1,63</t>
+          <t>-29,52; -0,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 2,54</t>
+          <t>-44,09; 2,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,23; -15,41</t>
+          <t>-56,22; -14,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 4,98</t>
+          <t>-57,16; -1,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-81,7; 7,91</t>
+          <t>-80,38; 15,52</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 1,22</t>
+          <t>-18,96; -0,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 5,46</t>
+          <t>-13,88; 4,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,85; -2,08</t>
+          <t>-39,49; -2,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 2,48</t>
+          <t>-31,51; -0,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 13,66</t>
+          <t>-28,88; 10,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,18; -7,86</t>
+          <t>-76,32; -7,25</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 12,74</t>
+          <t>-10,88; 12,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 1,78</t>
+          <t>-23,13; -0,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 22,81</t>
+          <t>-15,71; 23,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 29,95</t>
+          <t>-20,08; 29,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 3,7</t>
+          <t>-43,85; -0,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 56,98</t>
+          <t>-30,31; 58,93</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 13,08</t>
+          <t>-18,68; 16,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,9; 7,21</t>
+          <t>-25,93; 8,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,08; -6,66</t>
+          <t>-46,2; -8,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 28,82</t>
+          <t>-31,55; 36,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 17,87</t>
+          <t>-46,61; 19,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,23; -14,09</t>
+          <t>-90,04; -24,15</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,62; -3,21</t>
+          <t>-13,72; -3,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,14; -4,78</t>
+          <t>-15,33; -4,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,95; -5,24</t>
+          <t>-23,49; -5,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,97; -5,96</t>
+          <t>-24,54; -6,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,15; -11,16</t>
+          <t>-32,7; -10,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-53,53; -14,15</t>
+          <t>-54,24; -13,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Clase-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 11,71</t>
+          <t>-16,35; 12,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 4,0</t>
+          <t>-25,11; 4,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 22,09</t>
+          <t>-10,92; 21,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 28,21</t>
+          <t>-30,01; 29,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 10,14</t>
+          <t>-48,14; 11,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,57; 138,77</t>
+          <t>-34,41; 127,53</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,66; -1,5</t>
+          <t>-27,88; -1,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,24; -4,27</t>
+          <t>-28,18; -4,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,47; -1,76</t>
+          <t>-34,33; 0,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,44; -3,25</t>
+          <t>-44,93; -0,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,78; -11,84</t>
+          <t>-65,16; -12,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,76; -3,58</t>
+          <t>-69,21; 3,62</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-36,81; -6,92</t>
+          <t>-36,3; -8,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-29,52; -0,44</t>
+          <t>-30,48; 0,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 2,73</t>
+          <t>-43,16; 1,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,22; -14,62</t>
+          <t>-55,37; -14,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,16; -1,13</t>
+          <t>-57,23; 1,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-80,38; 15,52</t>
+          <t>-81,33; 6,8</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,96; -0,14</t>
+          <t>-20,1; -0,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 4,35</t>
+          <t>-12,92; 5,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,49; -2,84</t>
+          <t>-38,94; -3,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,51; -0,37</t>
+          <t>-32,06; -1,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 10,55</t>
+          <t>-26,71; 13,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,32; -7,25</t>
+          <t>-75,94; -8,94</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 12,47</t>
+          <t>-10,71; 11,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,13; -0,22</t>
+          <t>-24,33; 0,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 23,64</t>
+          <t>-14,99; 23,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 29,53</t>
+          <t>-19,4; 26,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,85; -0,02</t>
+          <t>-43,52; 0,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 58,93</t>
+          <t>-30,15; 57,04</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 16,48</t>
+          <t>-19,95; 15,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 8,27</t>
+          <t>-25,23; 7,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,2; -8,81</t>
+          <t>-47,3; -7,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 36,78</t>
+          <t>-33,61; 34,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 19,5</t>
+          <t>-45,51; 18,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,04; -24,15</t>
+          <t>-90,27; -17,8</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,72; -3,22</t>
+          <t>-13,77; -3,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,33; -4,62</t>
+          <t>-15,04; -4,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,49; -5,08</t>
+          <t>-22,75; -4,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,54; -6,23</t>
+          <t>-24,36; -6,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,7; -10,99</t>
+          <t>-32,08; -10,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-54,24; -13,16</t>
+          <t>-52,72; -12,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 12,24</t>
+          <t>-16,88; 12,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 4,25</t>
+          <t>-26,32; 3,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 21,31</t>
+          <t>-10,02; 23,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 29,68</t>
+          <t>-30,11; 29,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,14; 11,37</t>
+          <t>-50,14; 9,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 127,53</t>
+          <t>-33,72; 132,62</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-18,8</t>
+          <t>-20,18</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-45,16%</t>
+          <t>-47,16%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,88; -1,35</t>
+          <t>-29,77; -2,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,18; -4,53</t>
+          <t>-27,43; -3,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 0,42</t>
+          <t>-36,88; -2,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,93; -0,96</t>
+          <t>-46,95; -3,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,16; -12,14</t>
+          <t>-63,62; -8,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,21; 3,62</t>
+          <t>-72,01; -5,61</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-22,41</t>
+          <t>-23,31</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-50,58%</t>
+          <t>-50,32%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-36,3; -8,06</t>
+          <t>-36,87; -8,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 0,1</t>
+          <t>-31,32; 1,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,16; 1,52</t>
+          <t>-43,6; 2,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-55,37; -14,32</t>
+          <t>-56,23; -15,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 1,89</t>
+          <t>-57,19; 4,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-81,33; 6,8</t>
+          <t>-80,46; 7,24</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-18,75</t>
+          <t>-14,99</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-42,07%</t>
+          <t>-34,69%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,1; -0,69</t>
+          <t>-18,3; 1,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 5,19</t>
+          <t>-13,98; 5,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,94; -3,29</t>
+          <t>-28,22; -0,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,06; -1,1</t>
+          <t>-30,8; 2,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 13,6</t>
+          <t>-28,67; 13,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,94; -8,94</t>
+          <t>-56,53; -0,71</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>-0,27%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 11,49</t>
+          <t>-9,83; 12,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 0,1</t>
+          <t>-21,98; 1,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 23,48</t>
+          <t>-18,88; 17,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 26,81</t>
+          <t>-18,27; 29,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,52; 0,38</t>
+          <t>-41,63; 3,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 57,04</t>
+          <t>-34,51; 47,68</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-28,2</t>
+          <t>-31,37</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-66,65%</t>
+          <t>-70,28%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,95; 15,81</t>
+          <t>-21,16; 13,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 7,44</t>
+          <t>-26,9; 7,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,3; -7,59</t>
+          <t>-49,52; -9,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 34,15</t>
+          <t>-33,33; 28,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 18,32</t>
+          <t>-47,45; 17,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,27; -17,8</t>
+          <t>-89,12; -20,92</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-12,87</t>
+          <t>-12,62</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-31,55%</t>
+          <t>-30,92%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,77; -3,21</t>
+          <t>-13,62; -3,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,04; -4,7</t>
+          <t>-15,14; -4,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,75; -4,64</t>
+          <t>-19,87; -5,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,36; -6,12</t>
+          <t>-23,97; -5,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,08; -10,94</t>
+          <t>-32,15; -11,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-52,72; -12,59</t>
+          <t>-45,44; -15,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,58</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-11,16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,22%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-24,05%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.583000002128721</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-11.15874088485556</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.876452484710051</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.05217250237810511</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2405085357058444</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.239554564896241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-16,88; 12,01</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-26,32; 3,95</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,02; 23,57</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-30,11; 29,45</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-50,14; 9,19</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-33,72; 132,62</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-16.88336472680464</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-26.31918817645448</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.02191597006471</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.3011476742225255</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5014219759754615</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.33723811885554</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.01378629602728</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.947710769932997</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>23.56982356857495</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.2945418721289117</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.09189457926477983</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.326208648955535</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-15,27</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-16,62</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-20,18</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-27,31%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-44,86%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-47,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-29,77; -2,22</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-27,43; -3,53</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-36,88; -2,22</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-46,95; -3,82</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-63,62; -8,93</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-72,01; -5,61</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-15.26799273801434</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-16.61651124536176</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-20.18324094199964</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.2731303189360171</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4485825488933894</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4715769021950323</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-23,26</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-15,63</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-23,31</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-39,32%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-33,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-50,32%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-29.76818642473342</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-27.43451258665673</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-36.87985383296951</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.4694732318928578</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6361523507243801</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7200794832715403</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-36,87; -8,69</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-31,32; 1,63</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-43,6; 2,44</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-56,23; -15,41</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-57,19; 4,98</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-80,46; 7,24</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-2.215678758138645</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-3.527261165796124</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-2.215108359966846</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.03824196307641985</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.08931343232300701</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.05608969519714242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +767,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-9,02</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-4,41</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-14,99</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-16,14%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-9,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-34,69%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-23.25902538050713</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-15.63081618968711</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-23.30716819052626</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.3932239936491303</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.3359015848274122</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.5032265524900329</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-18,3; 1,22</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-13,98; 5,46</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-28,22; -0,15</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-30,8; 2,48</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-28,67; 13,66</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-56,53; -0,71</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-36.86735391009326</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-31.31540127408329</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-43.60042606245308</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.5622718193062587</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.571853083358602</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.8045774572578283</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-8.692460346100873</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.634332378952166</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.440657106216503</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-0.1541339799656115</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.04982514226934829</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.07243992762058631</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-11,69</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-24,52%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-9,83; 12,74</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-21,98; 1,78</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-18,88; 17,53</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-18,27; 29,95</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-41,63; 3,7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-34,51; 47,68</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-9.015100724750196</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-4.40542334383931</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-14.98993841753847</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.1614250435523673</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.09911237948765168</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3469253769875676</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-3,26</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-9,46</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-31,37</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-6,02%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-19,36%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-70,28%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-18.29751200210762</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-13.97533437648249</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-28.22136627879364</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.3080350948180547</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2867406871769271</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5652673733287853</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-21,16; 13,08</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-26,9; 7,21</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-49,52; -9,88</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-33,33; 28,82</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-47,45; 17,87</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-89,12; -20,92</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.219815360019311</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.464660618655872</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-0.1543612931979007</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.02480148654344615</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.136596688511711</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.007060765570742865</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +931,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-8,38</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-10,13</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-12,62</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-15,52%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-22,6%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-30,92%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>1.044626222431139</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-11.685158087871</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.124425946122958</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.02127491918569594</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2452264507122812</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.002664686695833483</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-13,62; -3,21</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-15,14; -4,78</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-19,87; -5,99</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-23,97; -5,96</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-32,15; -11,16</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-45,44; -15,97</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-9.832333333360973</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-21.98252029128523</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-18.88409300471343</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.1826752114479532</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4163442144738376</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3450654159325378</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>12.73730547086968</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.781553985384026</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>17.53391976744021</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.2994929098216421</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.03695454030572025</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.4767809679339715</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-3.264183035633694</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-9.459020198557361</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-31.37107843667569</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.06021069482639434</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.1936179143207115</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.7028369876372906</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-21.15598596241527</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-26.9042542793056</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-49.52079044344783</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.33332836410468</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.474481102011683</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.8911859037256851</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>13.07749604493186</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>7.205370290460341</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-9.884378479031016</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.2882360028896788</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1786882120347585</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-0.2092292926397957</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-8.378873265588444</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-10.12513238975394</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-12.62158440607503</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-0.1551503074314602</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.2259744216558496</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.3092378723581303</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-13.61772679137343</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-15.14371033017322</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-19.87453699425708</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.2396945479902867</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.3215174285873497</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.4543991895642183</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-3.206410664891312</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-4.777178817437712</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-5.991781035512196</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>-0.05956072459192538</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>-0.1116352497708145</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>-0.159745636300493</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1176,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_bre/IMC_inf_MED_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Clase-trans_bre.xlsx
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-2.583000002128721</v>
+        <v>-1.41095526586601</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-11.15874088485556</v>
+        <v>-7.682979865653278</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>5.876452484710051</v>
+        <v>3.740245928429287</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.05217250237810511</v>
+        <v>-0.02988398727658187</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.2405085357058444</v>
+        <v>-0.1784993820384984</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.239554564896241</v>
+        <v>0.1437484071010307</v>
       </c>
     </row>
     <row r="5">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-16.88336472680464</v>
+        <v>-15.4795151448587</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-26.31918817645448</v>
+        <v>-20.03146164782176</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-10.02191597006471</v>
+        <v>-12.19487944577734</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.3011476742225255</v>
+        <v>-0.2831621999487304</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.5014219759754615</v>
+        <v>-0.4105793066367528</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.33723811885554</v>
+        <v>-0.3884062031972321</v>
       </c>
     </row>
     <row r="6">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12.01378629602728</v>
+        <v>12.30855637471322</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>3.947710769932997</v>
+        <v>5.062428153787231</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>23.56982356857495</v>
+        <v>20.47384892558438</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.2945418721289117</v>
+        <v>0.3105470536653266</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.09189457926477983</v>
+        <v>0.149449802285301</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.326208648955535</v>
+        <v>1.121651988838638</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-15.26799273801434</v>
+        <v>-17.122281946918</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-16.61651124536176</v>
+        <v>-18.03016759064936</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-20.18324094199964</v>
+        <v>-21.00779555435843</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.2731303189360171</v>
+        <v>-0.3059117324799022</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.4485825488933894</v>
+        <v>-0.4685527061138883</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.4715769021950323</v>
+        <v>-0.4983882019432558</v>
       </c>
     </row>
     <row r="8">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-29.76818642473342</v>
+        <v>-29.78963005646383</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-27.43451258665673</v>
+        <v>-29.02656657776985</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-36.87985383296951</v>
+        <v>-38.48304596670954</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.4694732318928578</v>
+        <v>-0.4970419856068087</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.6361523507243801</v>
+        <v>-0.6570947957931967</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.7200794832715403</v>
+        <v>-0.7181806945315966</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-2.215678758138645</v>
+        <v>-2.853509402235314</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-3.527261165796124</v>
+        <v>-7.151162082144964</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-2.215108359966846</v>
+        <v>-3.899392582318342</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.03824196307641985</v>
+        <v>-0.06542955105331154</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.08931343232300701</v>
+        <v>-0.2165489516505796</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.05608969519714242</v>
+        <v>-0.04220444681834443</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-23.25902538050713</v>
+        <v>-20.99560208006318</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-15.63081618968711</v>
+        <v>-18.03378193607131</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-23.30716819052626</v>
+        <v>-19.16811271020511</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.3932239936491303</v>
+        <v>-0.365412536970719</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.3359015848274122</v>
+        <v>-0.3727704851786745</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.5032265524900329</v>
+        <v>-0.4379482459171956</v>
       </c>
     </row>
     <row r="11">
@@ -794,22 +794,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-36.86735391009326</v>
+        <v>-34.32111235245806</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-31.31540127408329</v>
+        <v>-31.87597332413629</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-43.60042606245308</v>
+        <v>-39.57132662042598</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.5622718193062587</v>
+        <v>-0.5467366896769266</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.571853083358602</v>
+        <v>-0.588236485151454</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.8045774572578283</v>
+        <v>-0.7533127746384681</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-8.692460346100873</v>
+        <v>-7.868330521216922</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1.634332378952166</v>
+        <v>-3.464662671285488</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2.440657106216503</v>
+        <v>3.875669958749207</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>-0.1541339799656115</v>
+        <v>-0.1444113314264713</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.04982514226934829</v>
+        <v>-0.08059459838389828</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.07243992762058631</v>
+        <v>0.1413157560686225</v>
       </c>
     </row>
     <row r="13">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-9.015100724750196</v>
+        <v>-8.663764176025735</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-4.40542334383931</v>
+        <v>-8.142986242641703</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-14.98993841753847</v>
+        <v>-14.8989392738502</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.1614250435523673</v>
+        <v>-0.1631374371064971</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.09911237948765168</v>
+        <v>-0.1758045979995663</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.3469253769875676</v>
+        <v>-0.3429806990176072</v>
       </c>
     </row>
     <row r="14">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-18.29751200210762</v>
+        <v>-16.85565169579984</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-13.97533437648249</v>
+        <v>-17.00941458831413</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-28.22136627879364</v>
+        <v>-28.43786992961188</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.3080350948180547</v>
+        <v>-0.2994298910266583</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.2867406871769271</v>
+        <v>-0.3481086444599354</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.5652673733287853</v>
+        <v>-0.5543886144770651</v>
       </c>
     </row>
     <row r="15">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1.219815360019311</v>
+        <v>0.4509642074046936</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>5.464660618655872</v>
+        <v>0.5098496017573485</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-0.1543612931979007</v>
+        <v>0.321180258480755</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.02480148654344615</v>
+        <v>0.008993358055434672</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.136596688511711</v>
+        <v>0.006165907382320685</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.007060765570742865</v>
+        <v>0.008239752859882401</v>
       </c>
     </row>
     <row r="16">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1.044626222431139</v>
+        <v>3.706493484665541</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-11.685158087871</v>
+        <v>-7.269087724401457</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-0.124425946122958</v>
+        <v>4.521583314500099</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.02127491918569594</v>
+        <v>0.07679198556115513</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.2452264507122812</v>
+        <v>-0.1660238250672919</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.002664686695833483</v>
+        <v>0.09724678551131632</v>
       </c>
     </row>
     <row r="17">
@@ -958,22 +958,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-9.832333333360973</v>
+        <v>-7.373429479778511</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-21.98252029128523</v>
+        <v>-18.89526432126823</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-18.88409300471343</v>
+        <v>-11.60122099184577</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.1826752114479532</v>
+        <v>-0.1366535820609719</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.4163442144738376</v>
+        <v>-0.3770907167193147</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.3450654159325378</v>
+        <v>-0.2316978809677074</v>
       </c>
     </row>
     <row r="18">
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>12.73730547086968</v>
+        <v>14.45153845767947</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1.781553985384026</v>
+        <v>3.619580455729567</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>17.53391976744021</v>
+        <v>21.88536965928985</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.2994929098216421</v>
+        <v>0.3413891787362893</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.03695454030572025</v>
+        <v>0.09843150599361508</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.4767809679339715</v>
+        <v>0.574687967797232</v>
       </c>
     </row>
     <row r="19">
@@ -1014,19 +1014,19 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>-3.264183035633694</v>
+        <v>0.1045073929061724</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>-9.459020198557361</v>
+        <v>-11.44388341952473</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>-31.37107843667569</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.06021069482639434</v>
+        <v>0.001954396036630688</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.1936179143207115</v>
+        <v>-0.2374463714754578</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>-0.7028369876372906</v>
@@ -1040,19 +1040,19 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>-21.15598596241527</v>
+        <v>-15.77356790771036</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>-26.9042542793056</v>
+        <v>-26.75465524027171</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>-49.52079044344783</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.33332836410468</v>
+        <v>-0.2589917881660717</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.474481102011683</v>
+        <v>-0.4819418688310721</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>-0.8911859037256851</v>
@@ -1066,19 +1066,19 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>13.07749604493186</v>
+        <v>16.31335414060857</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>7.205370290460341</v>
+        <v>4.465672691659289</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>-9.884378479031016</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.2882360028896788</v>
+        <v>0.3569034715993149</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.1786882120347585</v>
+        <v>0.1241426370563997</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>-0.2092292926397957</v>
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-8.378873265588444</v>
+        <v>-7.025249875730822</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-10.12513238975394</v>
+        <v>-10.6115983852892</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-12.62158440607503</v>
+        <v>-11.84256763582624</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.1551503074314602</v>
+        <v>-0.1342464620878902</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.2259744216558496</v>
+        <v>-0.2382654202803009</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.3092378723581303</v>
+        <v>-0.2901908591987468</v>
       </c>
     </row>
     <row r="23">
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-13.61772679137343</v>
+        <v>-11.6996630954015</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-15.14371033017322</v>
+        <v>-14.99452791770386</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-19.87453699425708</v>
+        <v>-18.52610460355464</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-0.2396945479902867</v>
+        <v>-0.2170779322533632</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.3215174285873497</v>
+        <v>-0.3232358938883949</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.4543991895642183</v>
+        <v>-0.4109044761140793</v>
       </c>
     </row>
     <row r="24">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>-3.206410664891312</v>
+        <v>-1.867712378683803</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>-4.777178817437712</v>
+        <v>-5.673687863945542</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-5.991781035512196</v>
+        <v>-4.582119342673301</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-0.05956072459192538</v>
+        <v>-0.03810091579393231</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.1116352497708145</v>
+        <v>-0.1341175275529676</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.159745636300493</v>
+        <v>-0.1211297444837917</v>
       </c>
     </row>
     <row r="25">
